--- a/output/laminas_comunales/comunal_p_monto_aps_a_2018_nuble.xlsx
+++ b/output/laminas_comunales/comunal_p_monto_aps_a_2018_nuble.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C442"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,67 +384,67 @@
         </is>
       </c>
       <c r="C2">
-        <v>77219.2109375</v>
+        <v>95396.328125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Portezuelo</t>
+          <t>El Carmen</t>
         </is>
       </c>
       <c r="C3">
-        <v>75731.40625</v>
+        <v>93926.0078125</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cobquecura</t>
+          <t>Portezuelo</t>
         </is>
       </c>
       <c r="C4">
-        <v>75606.984375</v>
+        <v>93231.9453125</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>El Carmen</t>
+          <t>Coihueco</t>
         </is>
       </c>
       <c r="C5">
-        <v>75441.6875</v>
+        <v>92182.984375</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Coihueco</t>
+          <t>Cobquecura</t>
         </is>
       </c>
       <c r="C6">
-        <v>74830.84375</v>
+        <v>91792.7109375</v>
       </c>
     </row>
     <row r="7">
@@ -459,112 +459,112 @@
         </is>
       </c>
       <c r="C7">
-        <v>72588.6015625</v>
+        <v>91215.9453125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>16303</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quillón</t>
+          <t>Ñiquén</t>
         </is>
       </c>
       <c r="C8">
-        <v>71742.3671875</v>
+        <v>89494.2578125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16303</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ñiquén</t>
+          <t>San Ignacio</t>
         </is>
       </c>
       <c r="C9">
-        <v>71283.359375</v>
+        <v>88177.0390625</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>San Carlos</t>
+          <t>San Nicolás</t>
         </is>
       </c>
       <c r="C10">
-        <v>71164.3984375</v>
+        <v>86971.8125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
+          <t>Quillón</t>
         </is>
       </c>
       <c r="C11">
-        <v>71036.953125</v>
+        <v>86825.8203125</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pinto</t>
+          <t>Pemuco</t>
         </is>
       </c>
       <c r="C12">
-        <v>70940</v>
+        <v>86147.3984375</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ranquil</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="C13">
-        <v>70911.140625</v>
+        <v>86055.6640625</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
+          <t>Pinto</t>
         </is>
       </c>
       <c r="C14">
-        <v>70840.953125</v>
+        <v>86002.46875</v>
       </c>
     </row>
     <row r="15">
@@ -579,112 +579,6412 @@
         </is>
       </c>
       <c r="C15">
-        <v>70559.40625</v>
+        <v>85904.375</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>16206</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chillán Viejo</t>
+          <t>Ranquil</t>
         </is>
       </c>
       <c r="C16">
-        <v>69478.390625</v>
+        <v>84973.0703125</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16105</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pemuco</t>
+          <t>Chillán Viejo</t>
         </is>
       </c>
       <c r="C17">
-        <v>68736.7421875</v>
+        <v>83492.828125</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Coelemu</t>
+          <t>Cobquecura</t>
         </is>
       </c>
       <c r="C18">
-        <v>67623.8203125</v>
+        <v>82904.1796875</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chillán</t>
+          <t>Portezuelo</t>
         </is>
       </c>
       <c r="C19">
-        <v>67199.6953125</v>
+        <v>81874.8515625</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16201</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Quirihue</t>
+          <t>San Fabián</t>
         </is>
       </c>
       <c r="C20">
-        <v>66238.0234375</v>
+        <v>81553.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bulnes</t>
+          <t>Cobquecura</t>
         </is>
       </c>
       <c r="C21">
-        <v>65797.984375</v>
+        <v>81491.75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>81442.765625</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>81078.6796875</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>80962.9296875</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>80244.1015625</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>80220.1328125</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>80212.2109375</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>79527.5078125</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>16109</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Yungay</t>
         </is>
       </c>
-      <c r="C22">
+      <c r="C29">
+        <v>79331.0625</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>78610.7421875</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>78458.0625</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>78456.4453125</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>77307.875</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>77219.2109375</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>77056.0546875</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>76698.703125</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>76035.6796875</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>75840.46875</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>75731.40625</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>75606.984375</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>75459.75</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>75441.6875</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>75016.3046875</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>74830.84375</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>74667.25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>74620.8828125</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>74529.6171875</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>74494.4453125</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>74435.5234375</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>74426.5390625</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>74389.6796875</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>73889.78125</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>73687.390625</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>73363.859375</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>73076.3984375</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>72777.6796875</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>72764.96875</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>72588.6015625</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>72455.796875</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>72166.8125</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>71742.3671875</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>71677.3046875</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>71283.359375</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>71190.828125</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>71164.3984375</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>71036.953125</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>70940</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>70934.5546875</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>70911.140625</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>70862.484375</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>70840.953125</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>70559.40625</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>70380.9140625</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>70295.2421875</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>70122.4921875</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>69831.7109375</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>69478.390625</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>69451.3125</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>68736.7421875</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>68673.5859375</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>68560.8671875</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>68459.671875</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>68296.328125</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>68124.6796875</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>68105.953125</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>67967.4296875</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>67745.875</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>67623.8203125</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>67524.65625</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>67443.7109375</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>67412.0625</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>67316.15625</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>67223.7109375</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>67199.6953125</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>67130.328125</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>67026.0703125</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>66679.7890625</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>66392.546875</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>66238.0234375</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>66200.59375</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>65999.84375</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>65844.265625</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>65797.984375</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>65735.796875</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C105">
         <v>65436.16796875</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>65158.73046875</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>65040.84765625</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>64947.28125</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>64904.69921875</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>64686.92578125</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>64407.1875</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>63944.3359375</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>63911.4375</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>63729.2421875</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>63600.17578125</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>63410.49609375</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>62670.6015625</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>62015.85546875</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>61982.26171875</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>61961.47265625</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>61903.2421875</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>61655.2578125</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>60923.87109375</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>60462.43359375</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>59092.49609375</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>59089.8515625</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>58517.359375</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>58459.4765625</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>57412.9453125</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>57315.40234375</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>57205.4453125</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>56427.63671875</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>56407.97265625</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>55948.5625</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>55894.65625</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>55714.0234375</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>55708.12109375</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>55510.62890625</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>55330.15234375</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>55325.80078125</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>54978.0546875</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>54316.421875</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>54138.4375</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>54070.765625</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>53934.87890625</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>53926.953125</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>53309.5078125</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>52896.51171875</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>56.7233390808105</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>56.7164192199707</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>56.3570785522461</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>56.1797752380371</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>55.9533081054688</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>55.477855682373</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>54.2056083679199</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>53.5013999938965</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>53.4172668457031</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>53.4050178527832</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>53.0546607971191</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>52.3680648803711</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>52.2727279663086</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>52.0934753417969</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>51.9607849121094</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>51.449275970459</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>51.4066505432129</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>51.2974052429199</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>51.2461051940918</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>51.2428283691406</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>51.0044631958008</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>50.8771934509277</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>50.7645263671875</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>50.3802299499512</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>50.3794708251953</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>50.3267974853516</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>49.8665237426758</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>49.7829246520996</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>49.7764549255371</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>49.2462310791016</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>48.9983291625977</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>48.8294296264649</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>48.8047790527344</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>48.6097793579102</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>48.4444427490234</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>48.0083847045898</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>47.8764495849609</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>47.4063415527344</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>47.3895568847656</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>47.2789115905762</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>47.2622489929199</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>47.0899467468262</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>47.0833854675293</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>46.7908897399902</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>46.718147277832</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>46.537841796875</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>46.4435157775879</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>46.4285697937012</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>46.3694267272949</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>46.1538467407227</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>46.1356086730957</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>46.1147804260254</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>46.082950592041</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>46.0543327331543</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>45.961540222168</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>45.8506240844727</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>45.8498039245605</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>45.8464775085449</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>45.8394165039062</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>45.7627105712891</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>45.7278480529785</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>45.7187004089355</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>45.6642074584961</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>45.6352806091309</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>45.5531463623047</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>45.546558380127</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>45.522388458252</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>45.4394683837891</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>45.2538642883301</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>45.2317886352539</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>45.1713409423828</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>44.9386520385742</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>44.9308738708496</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>44.9192771911621</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>44.795223236084</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>44.7752113342285</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>44.7261657714844</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>44.7123031616211</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>44.6674537658691</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>44.4504585266113</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>44.3883285522461</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>44.0970001220703</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>43.9004821777344</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>43.75</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>43.7346420288086</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>43.6800003051758</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>43.6438179016113</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>43.520191192627</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>43.2835807800293</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>43.2085571289062</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>43.146068572998</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>43.0340576171875</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>42.9095344543457</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>42.8571434020996</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>42.7912712097168</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>42.7751693725586</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>42.7156982421875</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>42.6805229187012</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C248">
+        <v>42.6356582641602</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C249">
+        <v>42.528736114502</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C250">
+        <v>42.5170059204102</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C251">
+        <v>42.5016098022461</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C252">
+        <v>42.4623107910156</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C253">
+        <v>42.3604774475098</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C254">
+        <v>42.2515068054199</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C255">
+        <v>42.1985816955566</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C256">
+        <v>42.1578407287598</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C257">
+        <v>42.1568641662598</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C258">
+        <v>42.1472396850586</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C259">
+        <v>42.0997772216797</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C260">
+        <v>42.0485191345215</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C261">
+        <v>42.0316886901855</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C262">
+        <v>41.7808227539062</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C263">
+        <v>41.5783271789551</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C264">
+        <v>41.5254249572754</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C265">
+        <v>41.392650604248</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C266">
+        <v>41.3551406860351</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C267">
+        <v>41.3373870849609</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C268">
+        <v>41.309253692627</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C269">
+        <v>41.2863082885742</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C270">
+        <v>41.2772598266602</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C271">
+        <v>41.1902885437012</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C272">
+        <v>41.1016960144043</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>41.0997200012207</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C274">
+        <v>41.0835227966309</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C275">
+        <v>41.069221496582</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C276">
+        <v>41.0606079101562</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C277">
+        <v>40.9356727600098</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C278">
+        <v>40.9338531494141</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C279">
+        <v>40.9326438903809</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C280">
+        <v>40.9326438903809</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C281">
+        <v>40.8805046081543</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C282">
+        <v>40.7713508605957</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C283">
+        <v>40.7004814147949</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C284">
+        <v>40.4958686828613</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C285">
+        <v>40.4858283996582</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C286">
+        <v>40.3501930236816</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C287">
+        <v>40.3100776672363</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C288">
+        <v>40.1754379272461</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C289">
+        <v>40.1484489440918</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C290">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C291">
+        <v>39.9892921447754</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C292">
+        <v>39.9750938415527</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C293">
+        <v>39.8359680175781</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C294">
+        <v>39.7859916687012</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C295">
+        <v>39.7637786865234</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C296">
+        <v>39.7515525817871</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C297">
+        <v>39.7196273803711</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C298">
+        <v>39.6414337158203</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C299">
+        <v>39.572193145752</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C300">
+        <v>39.4856262207031</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C301">
+        <v>39.3911437988281</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C302">
+        <v>39.308177947998</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C303">
+        <v>39.1240882873535</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C304">
+        <v>39.069766998291</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C305">
+        <v>38.8036804199219</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C306">
+        <v>38.7291984558105</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C307">
+        <v>38.7096786499023</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C308">
+        <v>38.625</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C309">
+        <v>38.4387359619141</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C310">
+        <v>38.2911376953125</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C311">
+        <v>38.2239379882812</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C312">
+        <v>38.2045936584473</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C313">
+        <v>38.1846618652344</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C314">
+        <v>38.0566787719727</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C315">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C316">
+        <v>37.9679145812988</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C317">
+        <v>37.9421234130859</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C318">
+        <v>37.8917388916016</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C319">
+        <v>37.7708969116211</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C320">
+        <v>37.698413848877</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C321">
+        <v>37.5280914306641</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C322">
+        <v>37.5215148925781</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C323">
+        <v>37.4239349365234</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C324">
+        <v>37.2486763000488</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C325">
+        <v>37.1007385253906</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C326">
+        <v>37.0203170776367</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C327">
+        <v>37.0090637207031</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C328">
+        <v>36.9281044006348</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C329">
+        <v>36.6920166015625</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C330">
+        <v>36.509635925293</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C331">
+        <v>36.3344039916992</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C332">
+        <v>36.1445770263672</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C333">
+        <v>35.9531784057617</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C334">
+        <v>35.9413185119629</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C335">
+        <v>35.9090919494629</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C336">
+        <v>35.8139533996582</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C337">
+        <v>35.6321830749512</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C338">
+        <v>35.4906044006348</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C339">
+        <v>35.4385948181152</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C340">
+        <v>35.4297676086426</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C341">
+        <v>35.3723411560059</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C342">
+        <v>35.1923065185547</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C343">
+        <v>35.0535545349121</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C344">
+        <v>34.7509651184082</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C345">
+        <v>34.7490348815918</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C346">
+        <v>34.6666679382324</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C347">
+        <v>34.5821342468262</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C348">
+        <v>34.5149269104004</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C349">
+        <v>34.3465042114258</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C350">
+        <v>34.307991027832</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C351">
+        <v>34.036434173584</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C352">
+        <v>33.9622650146484</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C353">
+        <v>33.9506187438965</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C354">
+        <v>33.8764228820801</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C355">
+        <v>33.3333320617676</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C356">
+        <v>33.183048248291</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C357">
+        <v>33.165828704834</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C358">
+        <v>33.1412086486816</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C359">
+        <v>33.0543937683105</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C360">
+        <v>32.9931983947754</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C361">
+        <v>32.8871879577637</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C362">
+        <v>32.8743553161621</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C363">
+        <v>32.859317779541</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C364">
+        <v>32.8099632263184</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C365">
+        <v>32.6885871887207</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C366">
+        <v>32.5763511657715</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C367">
+        <v>32.5581398010254</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C368">
+        <v>32.487922668457</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C369">
+        <v>32.3643417358398</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C370">
+        <v>32.1637420654297</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C371">
+        <v>32.1074981689453</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C372">
+        <v>31.8205528259277</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C373">
+        <v>31.7164173126221</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C374">
+        <v>31.4533615112305</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C375">
+        <v>31.4276885986328</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C376">
+        <v>31.3856430053711</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C377">
+        <v>31.3636360168457</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C378">
+        <v>31.3001613616943</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C379">
+        <v>31.2354316711426</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C380">
+        <v>31.1023616790771</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C381">
+        <v>31.0784931182861</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C382">
+        <v>30.8880310058594</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C383">
+        <v>30.5164318084717</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C384">
+        <v>30.2709064483643</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C385">
+        <v>30.2697296142578</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C386">
+        <v>30.2250804901123</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C387">
+        <v>29.8994979858398</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C388">
+        <v>29.6296291351318</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C389">
+        <v>29.5805740356445</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C390">
+        <v>29.4993228912354</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C391">
+        <v>29.3080062866211</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C392">
+        <v>29.0960445404053</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C393">
+        <v>28.7314777374268</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C394">
+        <v>28.6738357543945</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C395">
+        <v>28.555046081543</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C396">
+        <v>28.4420280456543</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C397">
+        <v>28.4046688079834</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C398">
+        <v>28.365385055542</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C399">
+        <v>28.2420749664307</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C400">
+        <v>28.235294342041</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C401">
+        <v>28.219970703125</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C402">
+        <v>28.1329917907715</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C403">
+        <v>27.7310924530029</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C404">
+        <v>27.5510196685791</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C405">
+        <v>27.3242626190186</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C406">
+        <v>27.3041477203369</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C407">
+        <v>27.0531406402588</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C408">
+        <v>26.8623027801514</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C409">
+        <v>26.7899475097656</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C410">
+        <v>26.7515926361084</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C411">
+        <v>26.7374515533447</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C412">
+        <v>26.4521675109863</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C413">
+        <v>26.0075035095215</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C414">
+        <v>25.8706474304199</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>16303</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Ñiquén</t>
+        </is>
+      </c>
+      <c r="C415">
+        <v>25.8532428741455</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C416">
+        <v>25.2241115570068</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C417">
+        <v>25.2126369476318</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C418">
+        <v>24.75</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C419">
+        <v>24.3604888916016</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C420">
+        <v>23.8021640777588</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C421">
+        <v>23.60475730896</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C422">
+        <v>23.5042743682861</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C423">
+        <v>23.2606430053711</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C424">
+        <v>23.0918502807617</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C425">
+        <v>22.9910717010498</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C426">
+        <v>22.3557167053223</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C427">
+        <v>22.0566310882568</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C428">
+        <v>21.226993560791</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C429">
+        <v>20.8637657165527</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Ranquil</t>
+        </is>
+      </c>
+      <c r="C430">
+        <v>19.9640293121338</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C431">
+        <v>19.6800003051758</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C432">
+        <v>19.674690246582</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C433">
+        <v>18.5071392059326</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C434">
+        <v>18.157543182373</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C435">
+        <v>16.9341888427734</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C436">
+        <v>16.7939910888672</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C437">
+        <v>16.7111587524414</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C438">
+        <v>16.6140899658203</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C439">
+        <v>15.5642023086548</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C440">
+        <v>15.1296825408936</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C441">
+        <v>14.9006624221802</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C442">
+        <v>10.5183849334717</v>
       </c>
     </row>
   </sheetData>
